--- a/AAII_Financials/Yearly/CBT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CBT_YR_FIN.xlsx
@@ -1128,13 +1128,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>3082000</v>
+        <v>3079000</v>
       </c>
       <c r="E17" s="3">
-        <v>3366000</v>
+        <v>3367000</v>
       </c>
       <c r="F17" s="3">
-        <v>3407000</v>
+        <v>3408000</v>
       </c>
       <c r="G17" s="3">
         <v>3753000</v>
@@ -1179,13 +1179,13 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>631000</v>
+        <v>634000</v>
       </c>
       <c r="E18" s="3">
-        <v>628000</v>
+        <v>627000</v>
       </c>
       <c r="F18" s="3">
-        <v>524000</v>
+        <v>523000</v>
       </c>
       <c r="G18" s="3">
         <v>568000</v>
@@ -1251,13 +1251,13 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-1000</v>
+        <v>2000</v>
       </c>
       <c r="E20" s="3">
-        <v>23000</v>
+        <v>22000</v>
       </c>
       <c r="F20" s="3">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="G20" s="3">
         <v>0</v>
@@ -1863,13 +1863,13 @@
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>1000</v>
+        <v>-2000</v>
       </c>
       <c r="E32" s="3">
-        <v>-23000</v>
+        <v>-22000</v>
       </c>
       <c r="F32" s="3">
-        <v>-11000</v>
+        <v>-10000</v>
       </c>
       <c r="G32" s="3">
         <v>0</v>
